--- a/samples/ss_gndul24_ingest.xlsx
+++ b/samples/ss_gndul24_ingest.xlsx
@@ -632,31 +632,21 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
         <is>
           <t>DKI Jakarta</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -703,27 +693,21 @@
       <c r="J3" t="n">
         <v>1</v>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
         <is>
           <t>DKI Jakarta</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -770,27 +754,21 @@
       <c r="J4" t="n">
         <v>1</v>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
         <is>
           <t>DKI Jakarta</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -819,35 +797,26 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
           <t>bus section + kopel</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
           <t>DKI Jakarta</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -876,31 +845,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
         <is>
           <t>DKI Jakarta</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -929,23 +888,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
           <t>bus coupler</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -961,7 +913,6 @@
           <t>DKI Jakarta</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -990,35 +941,26 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
           <t>aset milik KTT</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>Milik Pelanggan</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
           <t>DKI Jakarta</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1125,7 +1067,6 @@
       <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>SKTT 150 kV Gandul - Pondok Indah</t>
@@ -1146,7 +1087,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
         <v>2</v>
       </c>
@@ -1160,8 +1100,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>DKI Jakarta</t>
@@ -1178,7 +1116,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -1209,7 +1146,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>2</v>
       </c>
@@ -1223,8 +1159,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>DKI Jakarta</t>
@@ -1241,13 +1175,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>SUTT Pondok Indah - Sambas (aset milik KTT)</t>
@@ -1268,7 +1200,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>2</v>
       </c>
@@ -1282,8 +1213,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>DKI Jakarta</t>
@@ -1300,7 +1229,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1387,7 +1315,6 @@
           <t>GNDUL</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>150 kV</t>
@@ -1401,8 +1328,6 @@
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -1423,7 +1348,6 @@
           <t>GNDUL</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>150 kV</t>
@@ -1437,8 +1361,6 @@
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1459,7 +1381,6 @@
           <t>KMANG</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>150 kV</t>
@@ -1473,8 +1394,6 @@
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1495,7 +1414,6 @@
           <t>SAMBAS</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>150 kV</t>
@@ -1509,8 +1427,6 @@
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1584,7 +1500,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.Fleksibilitas Operasi antara Sub Sistem Gandul 2,4 dengan Sub Sistem Cawang 2,3-Depok 1 berkurang (Tidak bisa looping secara online saat pengalihan beban). 2.Tidak bisa sebagai jalur pemulihan jika terjadi gangguan pada salah satu sub sistem</t>
+          <t>1. Fleksibilitas Operasi antara Sub Sistem Gandul 2,4 dengan Sub Sistem Cawang 2,3-Depok 1 berkurang (Tidak bisa looping secara online saat pengalihan beban). 2. Tidak bisa sebagai jalur pemulihan jika terjadi gangguan pada salah satu sub sistem</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
